--- a/Result/checksun_type/基板.xlsx
+++ b/Result/checksun_type/基板.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>44.41</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>45.24</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>45.24</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>43.8</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>90702033.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>105746633.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>105746633</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>142323916.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>283181158.2</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>283181158.2</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-35659135.80271852</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>90702033</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>90702033.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>44.26000000000001</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>43.71</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>43.71</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>87525673.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>110801500.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>110801500.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>189373875.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>283370598.82</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>283370598.82</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-35489764.01778525</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>87525673</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>87525673.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>44.24999999999999</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>45.34</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>43.64</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>43.64</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>128580046.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>123016262.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>123016262.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>222414981.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>283171455.62</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>283171455.62</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-33639988.4672454</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>128580046</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>128580046.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>44.57</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>45.41</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>43.59</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>43.59</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>113653630.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>135354845.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>135354845.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>226837017.7</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>282518805.5</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>282518805.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-34194706.62835827</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>113653630</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>113653630.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>44.91</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>45.39</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>43.53</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>43.53</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>108271783.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>145615587.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>145615587.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>232423142.2</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>281761516.4</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>281761516.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-32166662.7646496</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>108271783</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>108271783.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>45.24</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>45.36</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>43.46</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>43.46</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>115976369.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>178901199.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>178901199.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>246879753.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>282984175.98</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>282984175.98</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-27544021.3963283</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>115976369</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>115976369.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>45.97</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>45.38</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>43.39</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>43.39</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>148599483.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>267946251.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>267946251.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>246572505.0</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>282049366.78</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>282049366.78</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-20782024.32028615</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>148599483</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>148599483.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>46.44</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>45.38</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>43.32</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>43.32</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>190272964.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>321813700.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>321813700.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>247253736.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>280836529.52</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>280836529.52</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-13875146.98593</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>190272964</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>190272964.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>46.62</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>45.34</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>43.23</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>43.23</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>164957337.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>318319189.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>318319189.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>250999781.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>282811790.16</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>282811790.16</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-7977654.223066568</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>164957337</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>164957337.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>46.52</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>45.31</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>43.15</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>45.31</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>43.15</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>274699843.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>319230697.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>319230697.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>284091819.4</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>289666457.52</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>289666457.52</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>3444640.267562151</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>274699843</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>274699843.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>46.35</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>45.14</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>43.08</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>43.08</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>561201630.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>314858307.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>314858307.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>295191794.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>297124608.34</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>297124608.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>7881055.316047311</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>561201630</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>561201630.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>24.1</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>24.82</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>26.62</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>24.82</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>26.62</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>1466251.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>1407130.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>1407130</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>1297897.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>2351746.94</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>2351746.94</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-94309.40015989356</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>1466251</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>1466251.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>24.04</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>24.87</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>26.69</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>26.69</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>1606907.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>1308869.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>1308869</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>1398342.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>2346796.78</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>2346796.78</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-109199.7364703822</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>1606907</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>1606907.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>24.15</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>24.95</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>26.77</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>26.77</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>1870858.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>1195451.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>1195451.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>1363722.3</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>2332586.26</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>2332586.26</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-141641.9406114239</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>1870858</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1870858.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>24.25</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>26.85</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>26.85</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>1370563.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>1096011.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>1096011.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>1524457.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>2317245.76</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>2317245.76</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-211209.7700767899</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>1370563</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>1370563.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>24.53</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>25.16</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>26.94</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>26.94</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>721071.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>988907.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>988907</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>1539434.9</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>2307674.0</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>2307674</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-249446.1418102845</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>721071</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>721071.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>24.79</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>25.26</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>27.02</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>27.02</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>974946.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1188664.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>1188664.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1574477.7</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>2313260.78</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>2313260.78</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-225572.3106506234</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>974946</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>974946.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>25.12</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>25.37</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>27.11</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>27.11</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1039821.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>1487816.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>1487816.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1508550.8</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>2309778.48</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>2309778.48</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-210611.576470728</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1039821</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1039821.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>25.12</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>25.46</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>27.18</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>27.18</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>1373656.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>1531992.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>1531992.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1484563.6</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>2319631.3</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>2319631.3</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-188668.149911209</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>1373656</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>1373656.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>25.09</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>25.58</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>27.25</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>27.25</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>835041.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>1952904.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>1952904.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1535294.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>2336878.2</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>2336878.2</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-186350.2851864956</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>835041</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>835041.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>25.04</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>27.32</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>27.32</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>1719859.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>2089962.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>2089962.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1612471.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>2365322.42</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>2365322.42</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-118674.9325373876</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1719859</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1719859.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>25.04</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>25.81</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>27.4</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>27.4</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>2470704.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1960290.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1960290.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1697767.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>2432026.4</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>2432026.4</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-112559.3954480409</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>2470704</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>2470704.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>121.5</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>123.98</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>119.29</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>123.98</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>119.29</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>116792257.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>156567321.4</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>156567321.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>189454064.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>318150407.34</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>318150407.34</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-35640807.2288911</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>116792257</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>116792257.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>121.3</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>123.78</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>119.06</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>123.78</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>119.06</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>143570356.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>190225454.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>190225454.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>215742345.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>318733821.76</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>318733821.76</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-33370636.02417654</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>143570356</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>143570356.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>120.8</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>123.58</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>118.88</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>123.58</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>118.88</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>136096754.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>206130143.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>206130143.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>221377285.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>318478020.68</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>318478020.68</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-31804807.90943512</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>136096754</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>136096754.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>121.3</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>123.58</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>118.73</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>123.58</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>118.73</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>166072395.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>203391625.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>203391625.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>240690842.7</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>318219735.08</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>318219735.08</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-27631281.53446758</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>166072395</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>166072395.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>122.3</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>123.58</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>118.63</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>123.58</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>118.63</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>220304845.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>213645726.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>213645726</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>249224824.6</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>318339495.48</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>318339495.48</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-23893945.33685437</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>220304845</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>220304845.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>123.6</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>123.42</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>118.47</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>123.42</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>118.47</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>285082922.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>222340807.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>222340807.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>250119491.9</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>316878790.8</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>316878790.8</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-23512158.07823354</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>285082922</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>285082922.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>124.6</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>123.1</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>118.31</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>123.1</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>118.31</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>223093801.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>241259236.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>241259236.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>251423710.6</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>315242401.56</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>315242401.56</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-29067536.02740973</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>223093801</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>223093801.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>125.6</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>122.78</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>118.16</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>122.78</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>118.16</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>122404164.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>236624427.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>236624427.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>278228999.2</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>313300516.2</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>313300516.2</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-29323972.41811109</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>122404164</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>122404164.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>126.0</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>122.28</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>117.91</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>122.28</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>117.91</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>217342898.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>277990060.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>277990060</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>338438970.1</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>312973362.38</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>312973362.38</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-17854849.99703753</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>217342898</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>217342898.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>125.4</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>121.6</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>117.66</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>117.66</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>263780252.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>284803923.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>284803923.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>409270685.2</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>312412010.72</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>312412010.72</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-11004723.39560974</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>263780252</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>263780252.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>125.2</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>120.62</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>117.36</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>120.62</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>117.36</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>379675068.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>277898176.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>277898176.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>437448534.2</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>311595701.46</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>311595701.46</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-5801233.20086962</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>379675068</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>379675068.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>46.72</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>48.78</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>53.85</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>48.78</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>53.85</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>36397.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>20578.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>20578</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>21715.6</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>63200.92</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>63200.92</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-1677.936188916665</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>36397</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>36397.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>46.2</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>49.0</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>49</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>54.1</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>10855.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>16345.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>16345.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>19807.4</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>69835.68</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>69835.67999999999</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-3450.42614723889</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>10855</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>10855.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>46.19</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>49.35</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>54.51</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>54.51</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>12469.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>22022.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>22022.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>21110.3</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>78674.28</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>78674.28</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-3122.682296726391</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>12469</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>12469.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>46.51000000000001</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>49.79</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>54.82</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>49.79</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>54.82</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>22895.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>21993.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>21993.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>22642.9</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>81870.78</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>81870.78</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-2715.880999682591</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>22895</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>22895.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>46.94</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>50.29</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>55.15</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>55.15</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>20274.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>22380.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>22380.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>22159.6</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>84937.42</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>84937.42</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-3154.811968202786</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>20274</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>20274.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>47.29</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>50.62</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>55.48</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>55.48</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>15235.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>22853.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>22853.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>21570.1</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>94318.52</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>94318.52</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-3388.362924367248</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>15235</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>15235.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>48.11</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>51.06</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>55.91</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>51.06</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>55.91</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>39238.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>23269.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>23269.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>22738.0</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>106149.06</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>106149.06</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-3061.101328731933</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>39238</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>39238.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>48.71</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>51.43</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>56.23</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>51.43</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>56.23</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>12325.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>20198.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>20198.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>21140.8</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>109157.5</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>109157.5</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-5056.009716083914</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>12325</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>12325.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>48.94</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>51.66</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>56.51</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>51.66</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>56.51</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>24830.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>23292.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>23292.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>21859.8</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>114023.04</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>114023.04</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-4841.771351012318</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>24830</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>24830.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>49.5</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>51.92</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>56.84</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>51.92</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>56.84</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>22638.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>21938.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>21938.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>21449.1</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>121201.54</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>121201.54</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-5702.617566945315</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>22638</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>22638.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>49.86</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>52.05</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>57.22</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>52.05</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>57.22</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>17315.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>20287.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>20287</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>21668.7</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>130303.7</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>130303.7</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-6493.875819458695</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>17315</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>17315.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>70.8</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>72.44</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>72.36</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>72.44</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>72.36</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>514324096.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>727462083.4</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>727462083.4</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>741826103.3</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>642056794.7</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>642056794.7</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>14031280.0420171</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>514324096</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>514324096.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>70.61999999999999</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>72.74</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>72.32</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>72.73999999999999</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>72.31999999999999</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>713580476.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>790130255.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>790130255</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>746061517.3</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>644083330.88</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>644083330.88</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>36964176.56141675</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>713580476</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>713580476.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>70.72</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>73.04</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>72.33</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>73.04000000000001</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>72.33</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>1151081202.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>819127894.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>819127894.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>727406878.6</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>639282663.44</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>639282663.4400001</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>47056410.28336561</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>1151081202</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>1151081202.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>71.03999999999999</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>73.33</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>72.33</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>72.33</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>695217391.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>729120942.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>729120942</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>647627836.0</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>623237776.08</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>623237776.08</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>12918223.16174376</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>695217391</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>695217391.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>71.58</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>73.58</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>72.33</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>73.58</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>72.33</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>563107252.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>703773325.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>703773325</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>633539795.2</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>615425122.3</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>615425122.3</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>12530570.48222172</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>563107252</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>563107252.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>71.96000000000001</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>73.84</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>73.84</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>72.3</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>827664954.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>756190123.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>756190123.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>624249429.1</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>608681996.76</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>608681996.76</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>25683918.31568241</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>827664954</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>827664954.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>72.42</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>74.1</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>72.3</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>858568672.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>701992779.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>701992779.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>579975619.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>597880131.24</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>597880131.24</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>15211664.35220897</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>858568672</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>858568672.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>72.84</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>74.3</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>72.27</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>72.27</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>701046441.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>635685863.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>635685863</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>541557952.6</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>583201064.82</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>583201064.8200001</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-3603084.822474718</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>701046441</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>701046441.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>72.92</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>74.4</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>72.21</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>72.20999999999999</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>568479306.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>566134730.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>566134730</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>517343108.1</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>572807232.94</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>572807232.9400001</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-13475234.43550599</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>568479306</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>568479306.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>72.74</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>74.32</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>72.12</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>74.31999999999999</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>72.12</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>825191243.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>563306265.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>563306265.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>529598359.0</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>568345964.76</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>568345964.76</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-12893425.33142543</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>825191243</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>825191243.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>72.84</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>74.22</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>72.05</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>74.22</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>72.05</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>556678236.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>492308735.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>492308735</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>514666289.8</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>558037094.4</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>558037094.4</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-39106640.38518798</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>556678236</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>556678236.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>51.21</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>53.08</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>57.02</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>53.08</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>57.02</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>18202.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>9349.4</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>9349.4</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>7989.3</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>13460.24</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>13460.24</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>500.6753961315808</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>18202</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>18202.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>50.71</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>53.27</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>57.18</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>53.27</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>57.18</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>17036.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>6987.2</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>6987.2</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>6636.3</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>14299.4</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>14299.4</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-325.7147088748216</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>17036</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>17036.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>50.42999999999999</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>53.55</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>57.46</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>57.46</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>2323.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>4899.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>4899.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>6022.3</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>15417.3</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>15417.3</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-1369.710762138438</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>2323</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>2323.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>50.73</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>53.94</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>57.69</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>53.94</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>57.69</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>3535.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>5598.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>5598</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>6458.6</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>15662.04</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>15662.04</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-1235.822596724375</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>3535</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>3535.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>51.26000000000001</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>54.33</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>57.9</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>57.9</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>5651.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>6317.6</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>6317.6</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>7375.3</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>15916.1</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>15916.1</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-1130.274410535557</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>5651</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>5651.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>51.94</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>54.7</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>58.1</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>6391.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>6629.2</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>6629.2</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>7233.5</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>16143.36</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>16143.36</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-1165.838629889547</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>6391</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>6391.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>52.62</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>55.11</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>58.29</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>58.29</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>6596.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>6285.4</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>6285.4</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>7319.0</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>16730.98</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>16730.98</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-1254.293277899191</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>6596</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>6596.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>53.27999999999999</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>55.51</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>58.53</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>55.51</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>58.53</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>5817.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>7145.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>7145.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>7601.0</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>17385.02</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>17385.02</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-1357.825157987996</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>5817</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>5817.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>53.73999999999999</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>55.81</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>58.76</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>55.81</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>58.76</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>7133.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>7319.2</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>7319.2</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>7839.6</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>19212.02</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>19212.02</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-1373.769802472432</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>7133</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>7133.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>53.96</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>56.14</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>59.1</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>59.1</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>7209.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>8433.0</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>8433</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>7485.2</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>23000.42</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>23000.42</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-1488.484658790469</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>7209</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>7209.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>53.86</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>56.38</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>59.37</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>59.37</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>4672.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>7837.8</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>7837.8</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>8182.9</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>23577.74</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>23577.74</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-1607.345715716578</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>4672</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>4672.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>135.2</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>135.22</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>128.41</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>135.22</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>128.41</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>1913931386.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>2078592970.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>2078592970</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>3415145986.7</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>2920853531.34</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>2920853531.34</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-179883407.5121007</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>1913931386</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>1913931386.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>134.5</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>135.28</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>127.74</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>135.28</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>127.74</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>1963910283.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>2437671745.0</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>2437671745</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>3349334206.6</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>2897386047.72</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>2897386047.72</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-135101686.3870907</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>1963910283</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>1963910283.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>136.1</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>135.28</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>127.11</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>135.28</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>127.11</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>1467837836.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>3549853380.4</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>3549853380.4</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>3238087001.1</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>2870727573.46</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>2870727573.46</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-71657620.65896654</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>1467837836</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>1467837836.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>138.0</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>136.1</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>126.55</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>136.1</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>126.55</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>1958235421.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>4076812661.6</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>4076812661.6</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>3187469141.5</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>2847620697.28</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>2847620697.28</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>74686579.01188803</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>1958235421</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>1958235421.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>139.6</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>136.9</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>126.04</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>136.9</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>126.04</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>3089049924.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>4333631835.8</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>4333631835.8</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>3063693168.6</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>2815155860.72</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>2815155860.72</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>228539745.184113</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>3089049924</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>3089049924.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>140.6</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>137.25</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>125.31</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>137.25</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>125.31</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>3709325261.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>4751699003.4</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>4751699003.4</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>2899708407.5</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>2760814634.22</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>2760814634.22</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>319009152.0664301</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>3709325261</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>3709325261.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>140.0</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>138.02</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>124.68</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>138.02</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>124.68</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>7524818460.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>4260996668.2</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>4260996668.2</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>2695993308.7</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>2696166918.84</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>2696166918.84</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>370399906.0745111</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>7524818460</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>7524818460.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>136.5</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>138.3</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>123.85</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>123.85</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>4102634242.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>2926320621.8</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>2926320621.8</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>2159067083.4</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>2553195032.84</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>2553195032.84</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>21783858.1191082</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>4102634242</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>4102634242.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>133.8</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>138.78</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>123.1</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>138.78</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>123.1</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>3242331292.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>2298125621.4</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>2298125621.4</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>2164732746.6</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>2484374040.96</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>2484374040.96</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-110354467.6785784</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>3242331292</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>3242331292.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>132.0</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>139.3</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>122.47</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>139.3</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>122.47</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>5179385762.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>1793754501.4</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>1793754501.4</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>1981624754.0</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>2445088871.22</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>2445088871.22</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-203006957.4724669</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>5179385762</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>5179385762.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>129.1</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>138.8</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>121.85</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>138.8</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>121.85</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>1255813585.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>1047717811.6</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>1047717811.6</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>1615857377.6</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>2368243976.26</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>2368243976.26</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-535658959.0540059</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>1255813585</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>1255813585.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34443,11 +33981,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
           <t>2459</t>
@@ -34629,41 +34163,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
+      <c r="AM79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO79" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN79" t="inlineStr">
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT79" t="inlineStr">
         <is>
           <t>0</t>
@@ -34684,20 +34214,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>0</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>0</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34240,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>0</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
